--- a/artfynd/A 33178-2025 artfynd.xlsx
+++ b/artfynd/A 33178-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379765</v>
+        <v>126379766</v>
       </c>
       <c r="B2" t="n">
-        <v>103794</v>
+        <v>97428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732141</v>
+        <v>732139</v>
       </c>
       <c r="R2" t="n">
-        <v>7292223</v>
+        <v>7292222</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379766</v>
+        <v>126379765</v>
       </c>
       <c r="B3" t="n">
-        <v>97428</v>
+        <v>103794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>732139</v>
+        <v>732141</v>
       </c>
       <c r="R3" t="n">
-        <v>7292222</v>
+        <v>7292223</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 33178-2025 artfynd.xlsx
+++ b/artfynd/A 33178-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126379766</v>
       </c>
       <c r="B2" t="n">
-        <v>97428</v>
+        <v>97437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>126379765</v>
       </c>
       <c r="B3" t="n">
-        <v>103794</v>
+        <v>103803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>126379767</v>
       </c>
       <c r="B4" t="n">
-        <v>91912</v>
+        <v>91915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -996,7 +996,7 @@
         <v>126379763</v>
       </c>
       <c r="B5" t="n">
-        <v>91260</v>
+        <v>91263</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
         <v>126379762</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 33178-2025 artfynd.xlsx
+++ b/artfynd/A 33178-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379766</v>
+        <v>126379765</v>
       </c>
       <c r="B2" t="n">
-        <v>97437</v>
+        <v>103803</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>222412</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732139</v>
+        <v>732141</v>
       </c>
       <c r="R2" t="n">
-        <v>7292222</v>
+        <v>7292223</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379765</v>
+        <v>126379766</v>
       </c>
       <c r="B3" t="n">
-        <v>103803</v>
+        <v>97437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>732141</v>
+        <v>732139</v>
       </c>
       <c r="R3" t="n">
-        <v>7292223</v>
+        <v>7292222</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 33178-2025 artfynd.xlsx
+++ b/artfynd/A 33178-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379765</v>
+        <v>126379766</v>
       </c>
       <c r="B2" t="n">
-        <v>103803</v>
+        <v>97437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222412</v>
+        <v>220250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732141</v>
+        <v>732139</v>
       </c>
       <c r="R2" t="n">
-        <v>7292223</v>
+        <v>7292222</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379766</v>
+        <v>126379765</v>
       </c>
       <c r="B3" t="n">
-        <v>97437</v>
+        <v>103803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>222412</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>732139</v>
+        <v>732141</v>
       </c>
       <c r="R3" t="n">
-        <v>7292222</v>
+        <v>7292223</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 33178-2025 artfynd.xlsx
+++ b/artfynd/A 33178-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>126379766</v>
+        <v>126379767</v>
       </c>
       <c r="B2" t="n">
-        <v>97437</v>
+        <v>92605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>898</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -714,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>732139</v>
+        <v>732138</v>
       </c>
       <c r="R2" t="n">
-        <v>7292222</v>
+        <v>7292216</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,32 +781,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126379765</v>
+        <v>126379762</v>
       </c>
       <c r="B3" t="n">
-        <v>103803</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222412</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>732141</v>
+        <v>732091</v>
       </c>
       <c r="R3" t="n">
-        <v>7292223</v>
+        <v>7292243</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,32 +887,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126379767</v>
+        <v>126379766</v>
       </c>
       <c r="B4" t="n">
-        <v>91915</v>
+        <v>98186</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>898</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -926,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>732138</v>
+        <v>732139</v>
       </c>
       <c r="R4" t="n">
-        <v>7292216</v>
+        <v>7292222</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,32 +993,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126379763</v>
+        <v>126379765</v>
       </c>
       <c r="B5" t="n">
-        <v>91263</v>
+        <v>104628</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>222412</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>732097</v>
+        <v>732141</v>
       </c>
       <c r="R5" t="n">
-        <v>7292248</v>
+        <v>7292223</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1096,112 +1096,6 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>126379762</v>
-      </c>
-      <c r="B6" t="n">
-        <v>80083</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Lobaria pulmonaria</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Grundsel, Pi lm</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>732091</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7292243</v>
-      </c>
-      <c r="S6" t="n">
-        <v>5</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Pite lappmark</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Arvidsjaur</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-06-09</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
